--- a/survey_templates/047_treasury_forecasting_accuracy_survey--survey_templates.xlsx
+++ b/survey_templates/047_treasury_forecasting_accuracy_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'skip'}</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Skip'}</t>
+          <t>Skip</t>
         </is>
       </c>
     </row>
